--- a/todo.xlsx
+++ b/todo.xlsx
@@ -1,127 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Répartition équilibrée" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>initialisation codeigniter 4</t>
-  </si>
-  <si>
-    <t>creation formulaire : login et inscription</t>
-  </si>
-  <si>
-    <t>login: email + mot de passe</t>
-  </si>
-  <si>
-    <t>inscription (2 pages): informations de l’utilisateur + informations de santé</t>
-  </si>
-  <si>
-    <t>page acant acceuil: Complétion du profil de l’utilisateur</t>
-  </si>
-  <si>
-    <t>choix d'objectif: _Augmenter son poids
-_ Réduire son poids
-_ Atteindre son IMC idéal</t>
-  </si>
-  <si>
-    <t>suggestion apres son choix:  les régimes et l’activité sportive nécessaire
-pendant une durée</t>
-  </si>
-  <si>
-    <t>creation du database (SQL)</t>
-  </si>
-  <si>
-    <t>code promo</t>
-  </si>
-  <si>
-    <t>FRONT OFFICE:</t>
-  </si>
-  <si>
-    <t>abonnement</t>
-  </si>
-  <si>
-    <t>BACK OFFICE:</t>
-  </si>
-  <si>
-    <t>authentification</t>
-  </si>
-  <si>
-    <t>Tableau de bord, statistiques</t>
-  </si>
-  <si>
-    <t>fonctionnalite:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_CRUD des régimes :  *Prix variant selon la durée  </t>
-  </si>
-  <si>
-    <t>*Chaque régime permet de varier le poids pendant une durée
-(en plus et en moins)</t>
-  </si>
-  <si>
-    <t>_CRUD des activités sportives</t>
-  </si>
-  <si>
-    <t>_Validation des codes pour le porte monnaie des utilisateurs</t>
-  </si>
-  <si>
-    <t>_CRUD des paramètres nécessaires</t>
-  </si>
-  <si>
-    <t>_CRUD des régimes
-* Pour constituer un régime, on doit mettre le % de viande, % de
-poisson, % de volaille</t>
-  </si>
-  <si>
-    <t>Données minimales
-/ 5 utilisateurs
-/ 15 codes
-/ 5 régimes
-/ 5 activités sportives</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="6"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -139,32 +49,87 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -206,7 +171,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -238,10 +203,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -273,7 +237,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -449,125 +412,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.109375" customWidth="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Personne</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tâches</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hery</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Base du projet</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Création base SQL; Initialisation CodeIgniter 4; Configuration projet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hery</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Authentification</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Login utilisateur; Inscription utilisateur; Sécurisation des accès</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hery</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gestion utilisateurs</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Complétion profil; Gestion abonnement; Validation codes promo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hery</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Données minimales</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5 utilisateurs; 15 codes promo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rolph</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Interfaces Front Office</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Page accueil; Profil utilisateur; Choix objectif</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rolph</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Suggestions &amp; affichage</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Affichage régimes; Activités sportives; Durée programmes; Prix</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rolph</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Responsive design; Thème graphique; Navigation utilisateur; Intégration formulaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rolph</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tests Front</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vérification mobile/desktop; Vérification navigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fenosoa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tableau de bord admin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Authentification admin; Dashboard; Statistiques</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fenosoa</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CRUD &amp; Administration</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CRUD régimes; CRUD activités sportives; CRUD paramètres</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fenosoa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Logique métier</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Calcul IMC; Recommandations régimes et activités; Durée recommandée</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fenosoa</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Données minimales</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5 régimes; 5 activités sportives</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fenosoa</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tests &amp; Validation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cohérence données; Validation fonctionnalités back office</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/todo.xlsx
+++ b/todo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>initialisation codeigniter 4</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>inscription (2 pages): informations de l’utilisateur + informations de santé</t>
-  </si>
-  <si>
-    <t>page acant acceuil: Complétion du profil de l’utilisateur</t>
   </si>
   <si>
     <t>choix d'objectif: _Augmenter son poids
@@ -90,6 +87,12 @@
 / 15 codes
 / 5 régimes
 / 5 activités sportives</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>page avant acceuil: Complétion du profil de l’utilisateur</t>
   </si>
 </sst>
 </file>
@@ -450,120 +453,141 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/todo.xlsx
+++ b/todo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>initialisation codeigniter 4</t>
   </si>
@@ -541,6 +541,9 @@
       <c r="A15" t="s">
         <v>11</v>
       </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">

--- a/todo.xlsx
+++ b/todo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>initialisation codeigniter 4</t>
   </si>
@@ -521,6 +521,9 @@
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">

--- a/todo.xlsx
+++ b/todo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>initialisation codeigniter 4</t>
   </si>
@@ -521,9 +521,6 @@
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">

--- a/todo.xlsx
+++ b/todo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t>initialisation codeigniter 4</t>
   </si>
@@ -529,6 +529,9 @@
       <c r="A10" t="s">
         <v>7</v>
       </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
